--- a/input/identifiers.xlsx
+++ b/input/identifiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk\Projects\test_works\web-harvest-service\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27AA567C-D230-4616-B672-051A81EBCC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3073DA-2FFB-4BBB-A521-59AA825F633B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0C804792-DBF2-4B10-9464-25E9537EA943}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{0C804792-DBF2-4B10-9464-25E9537EA943}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -434,12 +434,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>231138771115</v>
+        <v>231138771116</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>-231138771116</v>
+        <v>231138771115</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">

--- a/input/identifiers.xlsx
+++ b/input/identifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk\Projects\test_works\web-harvest-service\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E3073DA-2FFB-4BBB-A521-59AA825F633B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20C5C5E-C3B3-448D-911F-6CC5DF6487B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{0C804792-DBF2-4B10-9464-25E9537EA943}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>ИНН</t>
   </si>
@@ -421,105 +421,85 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD1EABF-4223-44B8-8EEF-D5A9B6393106}">
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.6640625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1">
+        <v>231138771116</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
-        <v>231138771116</v>
+        <v>231138771115</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
-        <v>231138771115</v>
+        <v>9102246754</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>9102246754</v>
+      <c r="A4" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
+      <c r="A5" s="1">
+        <v>266051268</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
-        <v>266051268</v>
+        <v>231138771120</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
-        <v>231138771120</v>
+        <v>3509005014</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>3509005014</v>
+        <v>231138771122</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>231138771122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1">
         <v>6147038999</v>
       </c>
     </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>4400007270</v>
+      </c>
+    </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1">
-        <v>4400007270</v>
+      <c r="A12" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>0</v>
+      <c r="A13" s="1">
+        <v>4625005426</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>4625005426</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
         <v>231138771128</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
-        <v>5404208780</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A17" s="1" t="s">
         <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1">
-        <v>5404208780</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>5404208780</v>
       </c>
     </row>
   </sheetData>

--- a/input/identifiers.xlsx
+++ b/input/identifiers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk\Projects\test_works\web-harvest-service\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E20C5C5E-C3B3-448D-911F-6CC5DF6487B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E024CD02-9310-4EB6-9309-067435587357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="17280" windowHeight="8880" xr2:uid="{0C804792-DBF2-4B10-9464-25E9537EA943}"/>
+    <workbookView xWindow="35490" yWindow="2955" windowWidth="17280" windowHeight="8880" xr2:uid="{0C804792-DBF2-4B10-9464-25E9537EA943}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD1EABF-4223-44B8-8EEF-D5A9B6393106}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.6640625" style="1" customWidth="1"/>
@@ -492,6 +492,11 @@
         <v>231138771128</v>
       </c>
     </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>4625005420</v>
+      </c>
+    </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>3</v>
@@ -500,6 +505,11 @@
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>4625005421</v>
       </c>
     </row>
   </sheetData>

--- a/input/identifiers.xlsx
+++ b/input/identifiers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\YandexDisk\Projects\test_works\web-harvest-service\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Igor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E024CD02-9310-4EB6-9309-067435587357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042AB158-840D-481C-BA5E-E1A7D528A7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35490" yWindow="2955" windowWidth="17280" windowHeight="8880" xr2:uid="{0C804792-DBF2-4B10-9464-25E9537EA943}"/>
   </bookViews>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD1EABF-4223-44B8-8EEF-D5A9B6393106}">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.6640625" style="1" customWidth="1"/>
@@ -472,6 +472,11 @@
         <v>6147038999</v>
       </c>
     </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>3</v>
+      </c>
+    </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4400007270</v>
@@ -498,18 +503,13 @@
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
-        <v>3</v>
+      <c r="A16" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
-        <v>4625005421</v>
+      <c r="A17" s="1">
+        <v>4625015421</v>
       </c>
     </row>
   </sheetData>

--- a/input/identifiers.xlsx
+++ b/input/identifiers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Igor\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042AB158-840D-481C-BA5E-E1A7D528A7ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5553BF-E3D8-4F0A-A49B-4A74B25767D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35490" yWindow="2955" windowWidth="17280" windowHeight="8880" xr2:uid="{0C804792-DBF2-4B10-9464-25E9537EA943}"/>
   </bookViews>
@@ -421,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AD1EABF-4223-44B8-8EEF-D5A9B6393106}">
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.6640625" style="1" customWidth="1"/>
@@ -462,54 +462,39 @@
         <v>3509005014</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>231138771122</v>
-      </c>
-    </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
-        <v>6147038999</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
-        <v>3</v>
+        <v>4400007270</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1">
-        <v>4400007270</v>
+      <c r="A11" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1">
+      <c r="A12" s="1">
         <v>4625005426</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
-        <v>231138771128</v>
+        <v>4625005420</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1">
-        <v>4625005420</v>
+      <c r="A15" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1">
-        <v>4625015421</v>
+      <c r="A16" s="1">
+        <v>4625005421</v>
       </c>
     </row>
   </sheetData>
